--- a/reports/集团总公司_利润表_2026-10.xlsx
+++ b/reports/集团总公司_利润表_2026-10.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>236915030</v>
+        <v>257840508</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>179912795</v>
+        <v>195451067</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1720520204</v>
+        <v>1868655645</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>733634</v>
+        <v>955749</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7115114</v>
+        <v>9215476</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>638060</v>
+        <v>835734</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>6173900</v>
+        <v>8064588</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>542033</v>
+        <v>704638</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5233171</v>
+        <v>6807687</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>497121</v>
+        <v>649369</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4813824</v>
+        <v>6283044</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>269802</v>
+        <v>356484</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2615809</v>
+        <v>3454671</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>216618</v>
+        <v>280440</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2093058</v>
+        <v>2720987</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>234017762</v>
+        <v>254058094</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>177015527</v>
+        <v>191668653</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>91375224</v>
+        <v>99531679</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>842239521</v>
+        <v>925576576</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1678533</v>
+        <v>2969044</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>16221590</v>
+        <v>28758850</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1514366</v>
+        <v>2161269</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>14651668</v>
+        <v>20915901</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>80647650</v>
+        <v>85612127</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>801889308</v>
+        <v>843636283</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1732471</v>
+        <v>2170391</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>16743320</v>
+        <v>20930268</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>759401</v>
+        <v>1085871</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>7326926</v>
+        <v>10468765</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2696350</v>
+        <v>3260966</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>26159968</v>
+        <v>31418731</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1187333</v>
+        <v>1628764</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>11509493</v>
+        <v>15709121</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>56824233</v>
+        <v>56487552</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>536409919</v>
+        <v>536454727</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>178002</v>
+        <v>175122</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1759589</v>
+        <v>1751974</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3438403</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>33295647</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2288364</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>22190197</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>175828502</v>
+        <v>197939080</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>141919003</v>
+        <v>149167543</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>112521816</v>
+        <v>119848453</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1066456554</v>
+        <v>1139762335</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>29397187</v>
+        <v>29319090</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>283617248</v>
+        <v>283401140</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5719293</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>55418982</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1833224</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>17736996</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1147780</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>11088689</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1379462</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>13310954</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1035690</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>9986648</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>690727</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>6659673</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>575404</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>5550723</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3202992</v>
+        <v>3196602</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>30879219</v>
+        <v>30894674</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1501127</v>
+        <v>1508169</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>14545646</v>
+        <v>14560699</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3878161</v>
+        <v>3880163</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>37662105</v>
+        <v>37669352</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>25289823</v>
+        <v>25097191</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>253702252</v>
+        <v>253651647</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>371294</v>
+        <v>3067076</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3638426</v>
+        <v>29795418</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1167229</v>
+        <v>1148925</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>11591908</v>
+        <v>11527879</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1214357</v>
+        <v>1098551</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>12012145</v>
+        <v>11014526</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>126607</v>
+        <v>123157</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1244457</v>
+        <v>1234874</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>490326</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>4908998</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>1002779</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>9700222</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>328011</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>3274463</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>246375</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2456776</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>411027</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>4096116</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1439008</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>13874748</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>219180</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>2185545</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>164203</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1639155</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>273242</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2731486</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>190933</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1911488</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136156</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1364846</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>108790</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>1091466</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81544</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>818334</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>58189260</v>
+        <v>59598685</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>63170586</v>
+        <v>63832340</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>572168</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>5542072</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136465</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1363964</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>221213</v>
+        <v>216655</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>2176560</v>
+        <v>2162487</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57968047</v>
+        <v>59954198</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7431047</v>
+        <v>7342083</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>73576693</v>
+        <v>73163982</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50537000</v>
+        <v>52612115</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50537000</v>
+        <v>52612115</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50537000</v>
+        <v>52612115</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50537000</v>
+        <v>52612115</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50537000</v>
+        <v>52612115</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
